--- a/spreadsheet/macrofree/wafsg_checklist.zh-Hant.xlsx
+++ b/spreadsheet/macrofree/wafsg_checklist.zh-Hant.xlsx
@@ -2240,7 +2240,11 @@
     <row r="46" ht="16.5" customHeight="1">
       <c r="A46" s="21" t="n"/>
       <c r="B46" s="21" t="n"/>
-      <c r="C46" s="21" t="n"/>
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>（應用服務計劃）對於較低的環境，請選擇Free （免費） 或 Basic （基本） 套餐。我們建議將這些層級用於實驗性用途。當您不再需要這些層時，請將其刪除。</t>
+        </is>
+      </c>
       <c r="D46" s="21" t="inlineStr">
         <is>
           <t>與更高級別相比，免費和基本級別對預算友好。它們為不需要高級計劃的全部功能和性能的非生產環境提供了經濟高效的解決方案。</t>
@@ -6011,7 +6015,11 @@
     <row r="167" ht="16.5" customHeight="1">
       <c r="A167" s="21" t="n"/>
       <c r="B167" s="21" t="n"/>
-      <c r="C167" s="21" t="n"/>
+      <c r="C167" s="21" t="inlineStr">
+        <is>
+          <t>在將小檔移動到較冷的層之前，先將它們打包成較大的檔。您可以使用 TAR 或 ZIP 等檔案格式。</t>
+        </is>
+      </c>
       <c r="D167" s="21" t="inlineStr">
         <is>
           <t>較冷的層具有較高的數據傳輸成本。通過減少大檔，可以減少傳輸數據所需的操作數。</t>
@@ -6174,7 +6182,11 @@
           <t>如果啟用軟刪除，請將經常被覆蓋的 blob 放入未啟用軟刪除的帳戶中。設置保留期。請考慮從較短的保留期開始，以更好地瞭解該功能如何影響您的帳單。建議的最短保留期為 7 天。</t>
         </is>
       </c>
-      <c r="D172" s="21" t="n"/>
+      <c r="D172" s="21" t="inlineStr">
+        <is>
+          <t>每次覆蓋 blob 時，都會創建一個新快照。容量費用增加的原因可能難以理解，因為這些快照的創建不會顯示在日誌中。為了降低容量費用，請將經常被覆蓋的數據存儲在禁用軟刪除的單獨存儲帳戶中。保留期可防止軟刪除的 blob 堆積並增加容量成本。</t>
+        </is>
+      </c>
       <c r="E172" s="21" t="n"/>
       <c r="F172" t="inlineStr">
         <is>
@@ -6229,7 +6241,11 @@
     <row r="174" ht="16.5" customHeight="1">
       <c r="A174" s="21" t="n"/>
       <c r="B174" s="21" t="n"/>
-      <c r="C174" s="21" t="n"/>
+      <c r="C174" s="21" t="inlineStr">
+        <is>
+          <t>禁用任何不需要的加密範圍，以避免不必要的費用。</t>
+        </is>
+      </c>
       <c r="D174" s="21" t="inlineStr">
         <is>
           <t>加密範圍按月收費。</t>
@@ -6369,7 +6385,11 @@
     <row r="179" ht="16.5" customHeight="1">
       <c r="A179" s="21" t="n"/>
       <c r="B179" s="21" t="n"/>
-      <c r="C179" s="21" t="n"/>
+      <c r="C179" s="21" t="inlineStr">
+        <is>
+          <t>使用基礎結構即代碼 （IaC） 在 Azure 資源管理器範本（ARM 範本）、Bicep 或 Terraform 中定義記憶體帳戶的詳細資訊。</t>
+        </is>
+      </c>
       <c r="D179" s="21" t="inlineStr">
         <is>
           <t>可以使用現有的 DevOps 流程來部署新的儲存帳戶，並使用 Azure Policy 強制實施其配置。</t>
